--- a/data/trans_dic/P33B_R4-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R4-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,4</t>
+          <t>8,28; 13,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,54</t>
+          <t>15,15; 21,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,73</t>
+          <t>12,1; 16,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,6</t>
+          <t>9,36; 15,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 23,55</t>
+          <t>16,62; 23,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 18,03</t>
+          <t>13,52; 17,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 20,74</t>
+          <t>14,93; 22,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,87; 30,76</t>
+          <t>19,97; 30,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 21,7</t>
+          <t>17,52; 23,49</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,14</t>
+          <t>13,43; 17,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 22,01</t>
+          <t>18,95; 23,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 18,43</t>
+          <t>16,45; 19,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,98</t>
+          <t>10,77; 17,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,6; 29,24</t>
+          <t>25,31; 30,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,8; 23,31</t>
+          <t>20,12; 24,06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,07</t>
+          <t>4,55; 15,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,19</t>
+          <t>20,26; 25,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,51; 21,65</t>
+          <t>17,56; 22,13</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,46</t>
+          <t>12,7; 15,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,77</t>
+          <t>21,59; 24,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,28</t>
+          <t>17,57; 19,33</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129057</t>
+          <t>146163</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39435; 67702</t>
+          <t>45608; 74831</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64279; 91895</t>
+          <t>74008; 104119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112535; 149815</t>
+          <t>125769; 170126</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75289</t>
+          <t>84132</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130373</t>
+          <t>142326</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42337; 70372</t>
+          <t>45117; 74291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62907; 90089</t>
+          <t>70336; 100119</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111614; 150334</t>
+          <t>122420; 162680</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80844</t>
+          <t>86667</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>134091</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30457; 138365</t>
+          <t>70246; 106614</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33169; 51334</t>
+          <t>37440; 56447</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52569; 180995</t>
+          <t>115278; 154627</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>161084</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>163502</t>
+          <t>183720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>359607</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>141000; 187758</t>
+          <t>152026; 202408</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81369; 215234</t>
+          <t>163110; 204694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206629; 370880</t>
+          <t>327763; 395550</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>77340</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>208959</t>
+          <t>229293</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275482</t>
+          <t>306634</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51318; 85232</t>
+          <t>61038; 96689</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156049; 245342</t>
+          <t>210096; 252652</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220614; 306109</t>
+          <t>281050; 336093</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>172817</t>
+          <t>191892</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190890</t>
+          <t>212133</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9027; 36247</t>
+          <t>10798; 35980</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>153584; 191629</t>
+          <t>170903; 213941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165341; 216813</t>
+          <t>189828; 239155</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>433239</t>
+          <t>476206</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>740383</t>
+          <t>824748</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1173621</t>
+          <t>1300954</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>350904; 487837</t>
+          <t>436945; 524056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>602193; 813728</t>
+          <t>784584; 872582</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1016272; 1270280</t>
+          <t>1242372; 1366943</t>
         </is>
       </c>
     </row>
